--- a/out/Attention-Mamba1_repeat_5_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>-0.0003952367915801005</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0.5087005382279433</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>1.018363782573382</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>-0.1174798635121967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0.3908254379241665</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0.3908254379241665</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0.3903145696725491</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>1.569497591829385</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>3.532435315056575</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>0.3003056796412886</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>2.56125850728476</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0.5260140958452942</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>3.31312810273621</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0.2880644608511745</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>3.362789536225332</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>0.11897481749706</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>3.312372729017776</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0.1482324128703972</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>3.489882706651934</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0.0892550600795171</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>3.520059823547435</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0.06785783994224731</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>3.566482303573357</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0.03001369920104128</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>3.558592012678458</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0.0238148356219502</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>3.576199698814032</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0.01180949128358974</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>3.57598383946685</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>0.006863622960431345</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>3.577898264978508</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>0.003430766080588488</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>3.577888987217805</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>0.001691042415805205</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>3.577841019013581</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0.0009796075694813073</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>3.578108763109853</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>0.0003253315768678424</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>3.577775672173265</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>0.0001611885448980572</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>3.577772511086111</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>8.550925681401474e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>3.577782245434689</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>3.766324804533871e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>3.577774375933364</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>2.118280671066587e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>3.577779597024105</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>7.887479732251461e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>3.577771259872736</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>9.151487243530285e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>3.577768155187487</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>3.577763836196337</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-1.724541871943372e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>3.577759012023448</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>3.577758154089863</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>3.577758382410898</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>3.577757586746686</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>3.577757649016059</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>3.577757676691335</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>3.577757828905359</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>3.577757482964397</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>3.577757559071409</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>3.57775772512307</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>3.577758084901671</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>3.577758105658128</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>3.577758209440417</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>3.577758437761451</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>3.577758313222705</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>3.577758340897982</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>3.577758396248536</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>3.577758659163667</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>3.577758576137836</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>3.57775836857326</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>3.577758382410898</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>3.577758520787282</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>3.577758237115694</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>3.577758064145213</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>3.577757960362924</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>3.577758105658128</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>3.577758347816802</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>3.57775817484632</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>3.577757877337093</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>3.577757863499455</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>3.577757496802036</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>3.577757496802036</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>3.577757434532663</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>3.577757330750374</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>3.577757157779894</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>3.577757206211628</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>3.577756846433028</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>3.577756804920113</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>3.577756860270667</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>3.57775691562122</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>3.577756957134136</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>3.577756687300186</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>3.57775674265074</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>3.577756887945943</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>3.577756853351847</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>3.577756839514209</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>3.577756929458858</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>3.577757247724543</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>3.577757067835243</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>3.577757109348159</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>3.57775692254004</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>3.577756991728232</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>3.577756791082475</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>3.577756832595389</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>3.577756860270667</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.008583858609199524</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.008654288947582245</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.009052358567714691</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.01012037694454193</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.00859890878200531</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.009595960378646851</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.008041791617870331</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.009754456579685211</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01000098139047623</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.008756004273891449</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.008205153048038483</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.007516182959079742</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.008879050612449646</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.007882960140705109</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.007585242390632629</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.007430501282215118</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.008269958198070526</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.008988894522190094</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01034390181303024</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.009048372507095337</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.008490376174449921</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.007945351302623749</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.007885538041591644</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.009738005697727203</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.008257366716861725</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01058929413557053</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01530223712325096</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01191155612468719</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0101943239569664</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01015087217092514</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.00887000560760498</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.008165419101715088</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.008705772459506989</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01219567656517029</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01027876883745193</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01004550606012344</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01091650128364563</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.009514838457107544</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.00989127904176712</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01092065870761871</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01308394223451614</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01446829363703728</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01946702972054482</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01689984276890755</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01178191602230072</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01408175379037857</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01407737284898758</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.2122727167830646</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.3661950314083699</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01182565093040466</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.9453922846818488</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.07006735519795214</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01556302607059479</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.718797248674785</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.1227294001466499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01453113928437233</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.8942234757282896</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.06721132397827324</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01488505676388741</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.9058105027624485</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.02775905880951137</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01263231039047241</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.8940472319822265</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.03458540515472364</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.02053675428032875</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.935464230815531</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.02082547197424655</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01217930763959885</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.9425053184761174</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.01583205915755942</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.02479028701782227</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.9533368633026545</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>0.007000599424997798</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.00970952957868576</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.951492997726175</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>0.005553954836411267</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.005780838429927826</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.9555982901916548</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>0.002751631250162162</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.03484558686614037</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.9555440911654862</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.001597969610841877</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.02040917053818703</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.9559869431489801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>0.0007950302050481237</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.009901680052280426</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.9559809470573687</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>0.0003917014464086749</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01052781194448471</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.9559659049587285</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.0002252980416752888</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01319992914795876</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.9560245909144622</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>7.088698387504487e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.008207090198993683</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.9559431116611959</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>3.317844950360773e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0106600895524025</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.9559385479517856</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.009229041635990143</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.9559371319825209</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01096693426370621</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.9559314351212175</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01204966753721237</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.9559291262164156</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.009718082845211029</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.9559231266828189</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01135378330945969</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.9559188840726649</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.007270246744155884</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.9559191123936995</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.008144952356815338</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.9559192023383496</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.007956661283969879</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.9559183444047648</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.00994449108839035</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01041007041931152</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.9559177770615876</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.008310765027999878</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.9559178393309608</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.008967302739620209</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.9559178670062376</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01038665324449539</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.9559180192202609</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.008336231112480164</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.9559176732792992</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.00889875739812851</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.9559177493863108</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.007465720176696777</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.9559179154379724</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01041218638420105</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.9559182752165725</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01085389405488968</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01122168451547623</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.9559183997553187</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.007565520703792572</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.9559186280763533</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.00704212486743927</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.9559185035376071</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.006314247846603394</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.9559185312128839</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.009546101093292236</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.955918586563438</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.007111668586730957</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.9559188494785686</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.007174111902713776</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.9559187664527379</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.006740622222423553</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.9559185588881611</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.006624504923820496</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.006423413753509521</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.9559187111021842</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.006382912397384644</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.9559184274305955</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.005909398198127747</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.9559182544601148</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.008026182651519775</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.9559181506778263</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.007135063409805298</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.006236724555492401</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.9559185381317034</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.006347797811031342</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.9559183651612224</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.006066255271434784</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.9559180676519955</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.006724931299686432</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.9559180538143569</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.006655320525169373</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.007317230105400085</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.009032242000102997</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.9559176248475646</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.006915107369422913</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.9559175210652762</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.007031388580799103</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.9559173480947953</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.00743277370929718</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.95591739652653</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.007247976958751678</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.9559170367479298</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.007078997790813446</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.9559169952350145</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.008005484938621521</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.006813660264015198</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.9559171059361221</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.006709732115268707</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.9559171474490376</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.006862767040729523</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.9559168776150875</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.007095754146575928</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.9559169329656414</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.006772525608539581</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.9559170782608453</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.006936080753803253</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.955917043666749</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.006595060229301453</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.9559170298291105</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.008682377636432648</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.9559171197737607</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01278684660792351</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.9559174380394453</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.008397877216339111</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.9559172581501452</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.007943585515022278</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.9559172996630606</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.008294381201267242</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.9559171128549413</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.007089748978614807</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.9559171820431338</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.00784505158662796</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.9559169813973759</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.007245279848575592</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.9559170229102913</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.00796595960855484</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.008583858609199524</v>
+        <v>0.008583851158618927</v>
       </c>
       <c r="JB2" t="n">
         <v>-1</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.008654288947582245</v>
+        <v>0.008654274046421051</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.8599999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.009052358567714691</v>
+        <v>0.009052366018295288</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.01012037694454193</v>
+        <v>0.01012039184570312</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.5799999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.00859890878200531</v>
+        <v>0.008598901331424713</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.5799999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.008041791617870331</v>
+        <v>0.008041784167289734</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.5799999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.009754456579685211</v>
+        <v>0.009754464030265808</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.01000098139047623</v>
+        <v>0.01000097393989563</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.008756004273891449</v>
+        <v>0.008755959570407867</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.1199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.008205153048038483</v>
+        <v>0.008205145597457886</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.8599999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.008879050612449646</v>
+        <v>0.008879072964191437</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.007882960140705109</v>
+        <v>0.007882967591285706</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.008988894522190094</v>
+        <v>0.0089888796210289</v>
       </c>
       <c r="JB19" t="n">
         <v>0.4399999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.01034390181303024</v>
+        <v>0.01034387946128845</v>
       </c>
       <c r="JB20" t="n">
         <v>0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.009048372507095337</v>
+        <v>0.009048342704772949</v>
       </c>
       <c r="JB21" t="n">
         <v>0.4399999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.008490376174449921</v>
+        <v>0.008490398526191711</v>
       </c>
       <c r="JB22" t="n">
         <v>0.16</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.007945351302623749</v>
+        <v>0.007945343852043152</v>
       </c>
       <c r="JB23" t="n">
         <v>0.02000000000000007</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.007885538041591644</v>
+        <v>0.007885530591011047</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.009738005697727203</v>
+        <v>0.009738020598888397</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.5799999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.008257366716861725</v>
+        <v>0.008257396519184113</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.01058929413557053</v>
+        <v>0.01058930158615112</v>
       </c>
       <c r="JB27" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.01530223712325096</v>
+        <v>0.01530225202441216</v>
       </c>
       <c r="JB28" t="n">
         <v>0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.01191155612468719</v>
+        <v>0.01191157102584839</v>
       </c>
       <c r="JB29" t="n">
         <v>0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.0101943239569664</v>
+        <v>0.01019433885812759</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.01015087217092514</v>
+        <v>0.01015086472034454</v>
       </c>
       <c r="JB31" t="n">
         <v>0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.00887000560760498</v>
+        <v>0.008870013058185577</v>
       </c>
       <c r="JB32" t="n">
         <v>0.16</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.008165419101715088</v>
+        <v>0.008165426552295685</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.008705772459506989</v>
+        <v>0.008705750107765198</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.01219567656517029</v>
+        <v>0.01219568401575089</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.01027876883745193</v>
+        <v>0.01027877628803253</v>
       </c>
       <c r="JB36" t="n">
         <v>0.1199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.01091650128364563</v>
+        <v>0.01091650873422623</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.009514838457107544</v>
+        <v>0.00951482355594635</v>
       </c>
       <c r="JB39" t="n">
         <v>0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.00989127904176712</v>
+        <v>0.009891293942928314</v>
       </c>
       <c r="JB40" t="n">
         <v>0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.01092065870761871</v>
+        <v>0.01092063635587692</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.01308394223451614</v>
+        <v>0.01308393105864525</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.01446829363703728</v>
+        <v>0.01446829736232758</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.01946702972054482</v>
+        <v>0.01946704462170601</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.01689984276890755</v>
+        <v>0.01689985021948814</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.01178191602230072</v>
+        <v>0.01178188621997833</v>
       </c>
       <c r="JB46" t="n">
         <v>0.8599999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.01408175379037857</v>
+        <v>0.01408177986741066</v>
       </c>
       <c r="JB47" t="n">
         <v>0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01407737284898758</v>
+        <v>0.01407739147543907</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.02000000000000007</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.01556302607059479</v>
+        <v>0.015563003718853</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.01453113928437233</v>
+        <v>0.01453114673495293</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.02000000000000007</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.01488505676388741</v>
+        <v>0.0148850604891777</v>
       </c>
       <c r="JB52" t="n">
         <v>0.1199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.01263231039047241</v>
+        <v>0.01263231411576271</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.02000000000000007</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.02053675428032875</v>
+        <v>0.02053676173090935</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.02000000000000007</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.02479028701782227</v>
+        <v>0.02479026094079018</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.00970952957868576</v>
+        <v>0.009709522128105164</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.005780838429927826</v>
+        <v>0.005780816078186035</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.1600000000000001</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.03484558686614037</v>
+        <v>0.03484560176730156</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.4399999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.02040917053818703</v>
+        <v>0.02040914446115494</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.4399999999999999</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.009901680052280426</v>
+        <v>0.00990169495344162</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
         <v>0.9559809470573687</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.01052781194448471</v>
+        <v>0.0105278417468071</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0.9559659049587285</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.01319992914795876</v>
+        <v>0.01319992542266846</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0.9560245909144622</v>
@@ -51824,7 +51824,7 @@
         <v>0.008207090198993683</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0.9559431116611959</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.0106600895524025</v>
+        <v>0.01066009700298309</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0.9559385479517856</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.009229041635990143</v>
+        <v>0.009229063987731934</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.01204966753721237</v>
+        <v>0.01204967498779297</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.009718082845211029</v>
+        <v>0.009718090295791626</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.01135378330945969</v>
+        <v>0.0113537609577179</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.007270246744155884</v>
+        <v>0.007270254194736481</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.008144952356815338</v>
+        <v>0.008144930005073547</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.007956661283969879</v>
+        <v>0.007956691086292267</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.00994449108839035</v>
+        <v>0.009944498538970947</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.01041007041931152</v>
+        <v>0.01041009277105331</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.008310765027999878</v>
+        <v>0.008310727775096893</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.008967302739620209</v>
+        <v>0.008967287838459015</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.01038665324449539</v>
+        <v>0.010386623442173</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.008336231112480164</v>
+        <v>0.00833623856306076</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.00889875739812851</v>
+        <v>0.008898749947547913</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.007465720176696777</v>
+        <v>0.00746571272611618</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.01041218638420105</v>
+        <v>0.01041220873594284</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0.9559182752165725</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.01085389405488968</v>
+        <v>0.01085394620895386</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0.9559182959730301</v>
@@ -67724,7 +67724,7 @@
         <v>0.01122168451547623</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0.9559183997553187</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.007565520703792572</v>
+        <v>0.007565505802631378</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0.9559186280763533</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.00704212486743927</v>
+        <v>0.007042132318019867</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0.9559185035376071</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.006314247846603394</v>
+        <v>0.00631425529718399</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3999999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.007174111902713776</v>
+        <v>0.007174104452133179</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.006740622222423553</v>
+        <v>0.00674062967300415</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.006624504923820496</v>
+        <v>0.006624512374401093</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.006423413753509521</v>
+        <v>0.006423406302928925</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.006382912397384644</v>
+        <v>0.006382904946804047</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.005909398198127747</v>
+        <v>0.005909420549869537</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.008026182651519775</v>
+        <v>0.008026190102100372</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.006236724555492401</v>
+        <v>0.006236732006072998</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.006724931299686432</v>
+        <v>0.006724901497364044</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.007317230105400085</v>
+        <v>0.007317207753658295</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.009032242000102997</v>
+        <v>0.009032249450683594</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.1199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.006915107369422913</v>
+        <v>0.006915092468261719</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.1199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.007031388580799103</v>
+        <v>0.007031381130218506</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.1199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.007247976958751678</v>
+        <v>0.007247984409332275</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.1199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.007078997790813446</v>
+        <v>0.007078982889652252</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.008005484938621521</v>
+        <v>0.008005499839782715</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.1199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.006813660264015198</v>
+        <v>0.006813712418079376</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.1199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.006862767040729523</v>
+        <v>0.006862752139568329</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.2599999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.007095754146575928</v>
+        <v>0.007095731794834137</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.1199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.006595060229301453</v>
+        <v>0.00659506767988205</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.01278684660792351</v>
+        <v>0.012786865234375</v>
       </c>
       <c r="JB119" t="n">
         <v>0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.008397877216339111</v>
+        <v>0.008397869765758514</v>
       </c>
       <c r="JB120" t="n">
         <v>0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.007943585515022278</v>
+        <v>0.007943592965602875</v>
       </c>
       <c r="JB121" t="n">
         <v>0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.008294381201267242</v>
+        <v>0.008294388651847839</v>
       </c>
       <c r="JB122" t="n">
         <v>0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.007089748978614807</v>
+        <v>0.007089726626873016</v>
       </c>
       <c r="JB123" t="n">
         <v>0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.00784505158662796</v>
+        <v>0.007845036685466766</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.007245279848575592</v>
+        <v>0.007245257496833801</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.3</v>
